--- a/配置文档/ItemConfig.xlsx
+++ b/配置文档/ItemConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lanran\Desktop\Gamedev\Roblox_Y1\配置文档\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GameDev\Roblox_Y1\配置文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
   <si>
     <t>子配置键</t>
   </si>
@@ -196,55 +196,64 @@
     <t>DisplayModelId</t>
   </si>
   <si>
-    <t>小周卡</t>
-  </si>
-  <si>
-    <t>立即获得100钻石,每天签到多获得30钻石(6天)</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/SmallWeekCard.png</t>
-  </si>
-  <si>
-    <t>大周卡</t>
-  </si>
-  <si>
-    <t>立即获得400钻石,每天签到多获得120钻石(6天)</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/GreatWeekCard.png</t>
-  </si>
-  <si>
-    <t>双倍出售卡</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/DoubleSaleCard.png</t>
-  </si>
-  <si>
-    <t>背包扩容卡(一小时)</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/TemporaryBackpackCard.png</t>
-  </si>
-  <si>
-    <t>力量卡(15分钟)</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/TrainingCard1.png</t>
-  </si>
-  <si>
-    <t>力量卡(30分钟)</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/TrainingCard2.png</t>
+    <t>Small Weekly Diamond Pass</t>
+  </si>
+  <si>
+    <t>Get 100 Diamonds instantly, plus 30 bonus Diamonds each day you check in for the next 6 days.</t>
+  </si>
+  <si>
+    <t>rbxassetid://131496626025159</t>
+  </si>
+  <si>
+    <t>Large Weekly Diamond Pass</t>
+  </si>
+  <si>
+    <t>Get 400 Diamonds instantly, plus 120 bonus Diamonds each day you check in for the next 6 days.</t>
+  </si>
+  <si>
+    <t>rbxassetid://106263117856612</t>
+  </si>
+  <si>
+    <t>Double Sell Value Card</t>
+  </si>
+  <si>
+    <t>Sell items for twice their normal value.</t>
+  </si>
+  <si>
+    <t>rbxassetid://116738678227555</t>
+  </si>
+  <si>
+    <t>Backpack Boost Card (1 Hour)</t>
+  </si>
+  <si>
+    <t>Increases backpack capacity for 1 hour.</t>
+  </si>
+  <si>
+    <t>rbxassetid://90071770389134</t>
+  </si>
+  <si>
+    <t>Strength Card (15 Minutes)</t>
+  </si>
+  <si>
+    <t>Instantly gain 15 minutes' worth of Strength.</t>
+  </si>
+  <si>
+    <t>rbxassetid://136097562202899</t>
+  </si>
+  <si>
+    <t>Strength Card (30 Minutes)</t>
+  </si>
+  <si>
+    <t>Instantly gain 30 minutes' worth of Strength.</t>
+  </si>
+  <si>
+    <t>rbxassetid://117314008364013</t>
   </si>
   <si>
     <t>NPC进度卡</t>
   </si>
   <si>
     <t>NPC任务进度加1</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/NpcCard.png</t>
   </si>
   <si>
     <t>KeyType, ValueType</t>
@@ -989,7 +998,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1033,9 +1042,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1365,125 +1371,125 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="23.45" customWidth="1"/>
-    <col min="3" max="3" width="27.0916666666667" customWidth="1"/>
-    <col min="4" max="4" width="29.3666666666667" customWidth="1"/>
-    <col min="5" max="5" width="31.8166666666667" customWidth="1"/>
+    <col min="2" max="2" width="23.4537037037037" customWidth="1"/>
+    <col min="3" max="3" width="27.0925925925926" customWidth="1"/>
+    <col min="4" max="4" width="29.3703703703704" customWidth="1"/>
+    <col min="5" max="5" width="31.8148148148148" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="22.5" spans="1:8">
-      <c r="A1" s="20" t="s">
+    <row r="1" customFormat="1" ht="22.2" spans="1:8">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" customFormat="1" ht="22.5" spans="1:8">
-      <c r="A2" s="20" t="s">
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" customFormat="1" ht="22.2" spans="1:8">
+      <c r="A2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="22.5" spans="1:8">
-      <c r="A3" s="20" t="s">
+    <row r="3" customFormat="1" ht="22.2" spans="1:8">
+      <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="22.5" spans="1:8">
-      <c r="A4" s="20" t="s">
+    <row r="4" customFormat="1" ht="22.2" spans="1:8">
+      <c r="A4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-    </row>
-    <row r="5" customFormat="1" ht="22.5" spans="1:8">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-    </row>
-    <row r="6" customFormat="1" ht="22.5" spans="1:8">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-    </row>
-    <row r="7" customFormat="1" ht="22.5" spans="1:8">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" customFormat="1" ht="22.2" spans="1:8">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" customFormat="1" ht="22.2" spans="1:8">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" customFormat="1" ht="22.2" spans="1:8">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1496,19 +1502,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G160"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.6333333333333" style="10" customWidth="1"/>
+    <col min="1" max="1" width="11.6296296296296" style="10" customWidth="1"/>
     <col min="2" max="2" width="35.5" style="10" customWidth="1"/>
-    <col min="3" max="3" width="11.9083333333333" style="10" customWidth="1"/>
-    <col min="4" max="5" width="24.6333333333333" style="10" customWidth="1"/>
-    <col min="6" max="6" width="33.7916666666667" style="10" customWidth="1"/>
+    <col min="3" max="3" width="11.9074074074074" style="10" customWidth="1"/>
+    <col min="4" max="4" width="43.9259259259259" style="10" customWidth="1"/>
+    <col min="5" max="5" width="24.6296296296296" style="10" customWidth="1"/>
+    <col min="6" max="6" width="33.7962962962963" style="10" customWidth="1"/>
     <col min="7" max="7" width="60.75" style="10" customWidth="1"/>
-    <col min="8" max="8" width="30.1416666666667" style="10" customWidth="1"/>
+    <col min="8" max="8" width="30.1388888888889" style="10" customWidth="1"/>
     <col min="9" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" ht="22.5" spans="1:7">
+    <row r="1" s="10" customFormat="1" ht="22.8" spans="1:7">
       <c r="A1" s="12" t="s">
         <v>16</v>
       </c>
@@ -1531,7 +1538,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" s="10" customFormat="1" ht="22.5" spans="1:7">
+    <row r="2" s="10" customFormat="1" ht="22.8" spans="1:7">
       <c r="A2" s="12" t="s">
         <v>8</v>
       </c>
@@ -1554,7 +1561,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" s="10" customFormat="1" ht="22.5" spans="1:7">
+    <row r="3" s="10" customFormat="1" ht="22.8" spans="1:7">
       <c r="A3" s="12" t="s">
         <v>28</v>
       </c>
@@ -1577,7 +1584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" s="10" customFormat="1" ht="22.5" spans="1:7">
+    <row r="4" s="10" customFormat="1" ht="22.8" spans="1:7">
       <c r="A4" s="13">
         <v>101</v>
       </c>
@@ -1598,7 +1605,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="5" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A5" s="14">
         <v>102</v>
       </c>
@@ -1619,7 +1626,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="6" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A6" s="14">
         <v>103</v>
       </c>
@@ -1634,7 +1641,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="7" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A7" s="14">
         <v>104</v>
       </c>
@@ -1655,7 +1662,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="8" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A8" s="14">
         <v>105</v>
       </c>
@@ -1676,7 +1683,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="9" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A9" s="14">
         <v>106</v>
       </c>
@@ -1697,732 +1704,732 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="10" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A10" s="14">
         <v>107</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="11">
         <v>1</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="11" t="s">
         <v>42</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="11" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A11" s="14"/>
     </row>
-    <row r="12" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="12" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A12" s="14"/>
     </row>
-    <row r="13" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="13" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A13" s="14"/>
     </row>
-    <row r="14" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="14" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A14" s="14"/>
     </row>
-    <row r="15" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="15" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A15" s="14"/>
     </row>
-    <row r="16" s="11" customFormat="1" ht="22.5" spans="1:7">
+    <row r="16" s="11" customFormat="1" ht="22.8" spans="1:7">
       <c r="A16" s="14"/>
     </row>
-    <row r="17" s="11" customFormat="1" ht="22.5" spans="1:1">
+    <row r="17" s="11" customFormat="1" ht="22.8" spans="1:1">
       <c r="A17" s="14"/>
     </row>
-    <row r="18" s="11" customFormat="1" ht="22.5" spans="1:1">
+    <row r="18" s="11" customFormat="1" ht="22.8" spans="1:1">
       <c r="A18" s="14"/>
     </row>
-    <row r="19" s="11" customFormat="1" ht="22.5" spans="1:1">
+    <row r="19" s="11" customFormat="1" ht="22.8" spans="1:1">
       <c r="A19" s="14"/>
     </row>
-    <row r="20" s="11" customFormat="1" ht="22.5" spans="1:1">
+    <row r="20" s="11" customFormat="1" ht="22.8" spans="1:1">
       <c r="A20" s="14"/>
     </row>
-    <row r="21" s="11" customFormat="1" ht="22.5" spans="1:1">
+    <row r="21" s="11" customFormat="1" ht="22.8" spans="1:1">
       <c r="A21" s="14"/>
     </row>
-    <row r="22" s="11" customFormat="1" ht="22.5" spans="1:1">
+    <row r="22" s="11" customFormat="1" ht="22.8" spans="1:1">
       <c r="A22" s="14"/>
     </row>
-    <row r="23" s="11" customFormat="1" ht="22.5" spans="1:1">
+    <row r="23" s="11" customFormat="1" ht="22.8" spans="1:1">
       <c r="A23" s="14"/>
     </row>
-    <row r="24" s="11" customFormat="1" ht="22.5" spans="1:1">
+    <row r="24" s="11" customFormat="1" ht="22.8" spans="1:1">
       <c r="A24" s="14"/>
     </row>
-    <row r="25" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="25" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A25" s="14"/>
     </row>
-    <row r="26" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="26" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A26" s="14"/>
     </row>
-    <row r="27" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="27" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A27" s="14"/>
     </row>
-    <row r="28" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="28" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A28" s="14"/>
     </row>
-    <row r="29" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="29" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A29" s="14"/>
     </row>
-    <row r="30" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="30" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A30" s="14"/>
     </row>
-    <row r="31" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="31" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A31" s="14"/>
     </row>
-    <row r="32" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="32" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A32" s="14"/>
     </row>
-    <row r="33" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="33" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A33" s="14"/>
     </row>
-    <row r="34" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="34" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A34" s="14"/>
     </row>
-    <row r="35" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="35" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A35" s="14"/>
     </row>
-    <row r="36" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="36" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A36" s="14"/>
     </row>
-    <row r="37" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="37" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A37" s="14"/>
     </row>
-    <row r="38" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="38" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A38" s="14"/>
     </row>
-    <row r="39" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="39" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A39" s="14"/>
     </row>
-    <row r="40" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="40" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A40" s="14"/>
     </row>
-    <row r="41" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="41" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A41" s="14"/>
     </row>
-    <row r="42" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="42" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A42" s="14"/>
     </row>
-    <row r="43" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="43" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A43" s="14"/>
     </row>
-    <row r="44" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="44" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A44" s="14"/>
     </row>
-    <row r="45" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="45" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A45" s="14"/>
     </row>
-    <row r="46" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="46" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A46" s="14"/>
     </row>
-    <row r="47" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="47" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A47" s="14"/>
     </row>
-    <row r="48" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="48" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A48" s="14"/>
     </row>
-    <row r="49" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="49" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A49" s="14"/>
     </row>
-    <row r="50" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="50" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A50" s="14"/>
     </row>
-    <row r="51" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="51" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A51" s="14"/>
     </row>
-    <row r="52" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="52" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A52" s="14"/>
     </row>
-    <row r="53" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="53" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A53" s="14"/>
     </row>
-    <row r="54" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="54" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A54" s="14"/>
     </row>
-    <row r="55" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="55" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A55" s="14"/>
     </row>
-    <row r="56" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="56" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A56" s="14"/>
     </row>
-    <row r="57" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="57" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A57" s="14"/>
     </row>
-    <row r="58" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="58" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A58" s="14"/>
     </row>
-    <row r="59" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="59" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A59" s="14"/>
     </row>
-    <row r="60" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="60" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A60" s="14"/>
     </row>
-    <row r="61" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="61" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A61" s="14"/>
     </row>
-    <row r="62" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="62" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A62" s="14"/>
     </row>
-    <row r="63" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="63" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A63" s="14"/>
     </row>
-    <row r="64" s="10" customFormat="1" ht="22.5" spans="1:1">
+    <row r="64" s="10" customFormat="1" ht="22.8" spans="1:1">
       <c r="A64" s="14"/>
     </row>
-    <row r="65" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="65" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A65" s="14"/>
     </row>
     <row r="66" s="10" customFormat="1" ht="16" customHeight="1" spans="1:6">
       <c r="A66" s="14"/>
     </row>
-    <row r="67" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="67" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A67" s="14"/>
     </row>
-    <row r="68" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="68" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A68" s="14"/>
     </row>
-    <row r="69" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="69" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A69" s="14"/>
     </row>
-    <row r="70" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="70" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A70" s="14"/>
     </row>
-    <row r="71" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="71" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A71" s="14"/>
     </row>
-    <row r="72" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="72" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A72" s="14"/>
     </row>
-    <row r="73" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="73" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A73" s="14"/>
     </row>
-    <row r="74" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="74" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A74" s="14"/>
     </row>
-    <row r="75" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="75" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A75" s="14"/>
     </row>
-    <row r="76" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A76" s="16"/>
-    </row>
-    <row r="77" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A77" s="16"/>
-    </row>
-    <row r="78" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="76" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A76" s="15"/>
+    </row>
+    <row r="77" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A77" s="15"/>
+    </row>
+    <row r="78" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="A78" s="14"/>
     </row>
-    <row r="80" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="80" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
       <c r="E80" s="14"/>
       <c r="F80" s="14"/>
     </row>
-    <row r="81" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="81" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
       <c r="E81" s="14"/>
       <c r="F81" s="14"/>
     </row>
-    <row r="82" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="82" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="14"/>
     </row>
-    <row r="83" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="83" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
       <c r="E83" s="14"/>
       <c r="F83" s="14"/>
     </row>
-    <row r="84" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="84" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
       <c r="E84" s="14"/>
       <c r="F84" s="14"/>
     </row>
-    <row r="85" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="85" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
       <c r="E85" s="14"/>
       <c r="F85" s="14"/>
     </row>
-    <row r="86" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="86" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
     </row>
-    <row r="87" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="87" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
       <c r="E87" s="14"/>
       <c r="F87" s="14"/>
     </row>
-    <row r="88" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="88" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="14"/>
     </row>
-    <row r="89" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="89" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="14"/>
     </row>
-    <row r="90" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="90" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
       <c r="E90" s="14"/>
       <c r="F90" s="14"/>
     </row>
-    <row r="91" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="91" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
       <c r="E91" s="14"/>
       <c r="F91" s="14"/>
     </row>
-    <row r="92" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="92" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
       <c r="E92" s="14"/>
       <c r="F92" s="14"/>
     </row>
-    <row r="93" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="93" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
       <c r="E93" s="14"/>
       <c r="F93" s="14"/>
     </row>
-    <row r="94" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="94" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
       <c r="E94" s="14"/>
       <c r="F94" s="14"/>
     </row>
-    <row r="95" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="95" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
-      <c r="F95" s="17"/>
-    </row>
-    <row r="96" s="10" customFormat="1" ht="22.5" spans="3:6">
+      <c r="F95" s="16"/>
+    </row>
+    <row r="96" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
-      <c r="F96" s="17"/>
-    </row>
-    <row r="97" s="10" customFormat="1" ht="22.5" spans="3:6">
+      <c r="F96" s="16"/>
+    </row>
+    <row r="97" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
       <c r="E97" s="14"/>
-      <c r="F97" s="17"/>
-    </row>
-    <row r="98" s="10" customFormat="1" ht="22.5" spans="3:6">
+      <c r="F97" s="16"/>
+    </row>
+    <row r="98" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
       <c r="E98" s="14"/>
       <c r="F98" s="14"/>
     </row>
-    <row r="99" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="99" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
       <c r="E99" s="14"/>
       <c r="F99" s="14"/>
     </row>
-    <row r="100" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="100" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
       <c r="E100" s="14"/>
       <c r="F100" s="14"/>
     </row>
-    <row r="101" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="101" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
       <c r="E101" s="14"/>
       <c r="F101" s="14"/>
     </row>
-    <row r="102" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="102" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
       <c r="F102" s="14"/>
     </row>
-    <row r="103" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="103" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
       <c r="E103" s="14"/>
       <c r="F103" s="14"/>
     </row>
-    <row r="104" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="104" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
       <c r="F104" s="14"/>
     </row>
-    <row r="105" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="105" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
       <c r="E105" s="14"/>
       <c r="F105" s="14"/>
     </row>
-    <row r="106" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="106" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
       <c r="E106" s="14"/>
       <c r="F106" s="14"/>
     </row>
-    <row r="107" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="107" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
       <c r="E107" s="14"/>
       <c r="F107" s="14"/>
     </row>
-    <row r="108" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="108" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
       <c r="F108" s="14"/>
     </row>
-    <row r="109" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="109" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
       <c r="F109" s="14"/>
     </row>
-    <row r="110" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="110" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
       <c r="E110" s="14"/>
       <c r="F110" s="14"/>
     </row>
-    <row r="111" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="111" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
       <c r="E111" s="14"/>
       <c r="F111" s="14"/>
     </row>
-    <row r="112" s="10" customFormat="1" ht="22.5" spans="3:6">
+    <row r="112" s="10" customFormat="1" ht="22.8" spans="3:6">
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
       <c r="E112" s="14"/>
       <c r="F112" s="14"/>
     </row>
-    <row r="113" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="113" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
       <c r="E113" s="14"/>
       <c r="F113" s="14"/>
     </row>
-    <row r="114" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="114" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
       <c r="E114" s="14"/>
       <c r="F114" s="14"/>
     </row>
-    <row r="115" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="115" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
       <c r="E115" s="14"/>
       <c r="F115" s="14"/>
     </row>
-    <row r="116" s="10" customFormat="1" ht="22.5" spans="1:6">
+    <row r="116" s="10" customFormat="1" ht="22.8" spans="1:6">
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
       <c r="E116" s="14"/>
       <c r="F116" s="14"/>
     </row>
-    <row r="117" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A117" s="16"/>
+    <row r="117" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A117" s="15"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
       <c r="E117" s="14"/>
       <c r="F117" s="14"/>
     </row>
-    <row r="118" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A118" s="16"/>
+    <row r="118" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A118" s="15"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
       <c r="E118" s="14"/>
       <c r="F118" s="14"/>
     </row>
-    <row r="119" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A119" s="16"/>
+    <row r="119" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A119" s="15"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
       <c r="D119" s="14"/>
       <c r="E119" s="14"/>
       <c r="F119" s="14"/>
     </row>
-    <row r="120" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A120" s="16"/>
+    <row r="120" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A120" s="15"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
       <c r="E120" s="14"/>
       <c r="F120" s="14"/>
     </row>
-    <row r="121" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A121" s="16"/>
+    <row r="121" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A121" s="15"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
       <c r="D121" s="14"/>
       <c r="E121" s="14"/>
       <c r="F121" s="14"/>
     </row>
-    <row r="122" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A122" s="16"/>
+    <row r="122" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A122" s="15"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
       <c r="E122" s="14"/>
       <c r="F122" s="14"/>
     </row>
-    <row r="123" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A123" s="16"/>
+    <row r="123" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A123" s="15"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
       <c r="D123" s="14"/>
       <c r="E123" s="14"/>
       <c r="F123" s="14"/>
     </row>
-    <row r="124" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A124" s="16"/>
+    <row r="124" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A124" s="15"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
       <c r="D124" s="14"/>
       <c r="E124" s="14"/>
       <c r="F124" s="14"/>
     </row>
-    <row r="125" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A125" s="16"/>
+    <row r="125" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A125" s="15"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
       <c r="D125" s="14"/>
       <c r="E125" s="14"/>
       <c r="F125" s="14"/>
     </row>
-    <row r="126" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A126" s="16"/>
+    <row r="126" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A126" s="15"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
       <c r="E126" s="14"/>
       <c r="F126" s="14"/>
     </row>
-    <row r="127" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A127" s="16"/>
+    <row r="127" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A127" s="15"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
       <c r="D127" s="14"/>
       <c r="E127" s="14"/>
       <c r="F127" s="14"/>
     </row>
-    <row r="128" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A128" s="16"/>
+    <row r="128" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A128" s="15"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
       <c r="E128" s="14"/>
       <c r="F128" s="14"/>
     </row>
-    <row r="129" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A129" s="16"/>
+    <row r="129" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A129" s="15"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
       <c r="E129" s="14"/>
       <c r="F129" s="14"/>
     </row>
-    <row r="130" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A130" s="16"/>
+    <row r="130" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A130" s="15"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
       <c r="E130" s="14"/>
       <c r="F130" s="14"/>
     </row>
-    <row r="131" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A131" s="16"/>
+    <row r="131" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A131" s="15"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
       <c r="E131" s="14"/>
       <c r="F131" s="14"/>
     </row>
-    <row r="132" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A132" s="16"/>
+    <row r="132" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A132" s="15"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
       <c r="D132" s="14"/>
       <c r="E132" s="14"/>
       <c r="F132" s="14"/>
     </row>
-    <row r="133" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A133" s="16"/>
+    <row r="133" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A133" s="15"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
       <c r="D133" s="14"/>
       <c r="E133" s="14"/>
       <c r="F133" s="14"/>
     </row>
-    <row r="134" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A134" s="16"/>
+    <row r="134" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A134" s="15"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
       <c r="D134" s="14"/>
       <c r="E134" s="14"/>
       <c r="F134" s="14"/>
     </row>
-    <row r="135" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A135" s="16"/>
+    <row r="135" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A135" s="15"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
       <c r="D135" s="14"/>
       <c r="E135" s="14"/>
       <c r="F135" s="14"/>
     </row>
-    <row r="136" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A136" s="16"/>
+    <row r="136" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A136" s="15"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
       <c r="D136" s="14"/>
       <c r="E136" s="14"/>
       <c r="F136" s="14"/>
     </row>
-    <row r="137" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A137" s="16"/>
+    <row r="137" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A137" s="15"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="14"/>
       <c r="E137" s="14"/>
       <c r="F137" s="14"/>
     </row>
-    <row r="138" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A138" s="16"/>
+    <row r="138" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A138" s="15"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
       <c r="E138" s="14"/>
     </row>
-    <row r="139" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A139" s="16"/>
+    <row r="139" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A139" s="15"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
       <c r="E139" s="14"/>
     </row>
-    <row r="140" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A140" s="18"/>
+    <row r="140" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A140" s="17"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
       <c r="E140" s="14"/>
     </row>
-    <row r="141" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A141" s="18"/>
+    <row r="141" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A141" s="17"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
       <c r="E141" s="14"/>
     </row>
-    <row r="142" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A142" s="18"/>
+    <row r="142" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A142" s="17"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
       <c r="E142" s="14"/>
     </row>
-    <row r="143" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A143" s="18"/>
+    <row r="143" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A143" s="17"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
       <c r="E143" s="14"/>
     </row>
-    <row r="144" s="10" customFormat="1" ht="22.5" spans="1:6">
-      <c r="A144" s="18"/>
+    <row r="144" s="10" customFormat="1" ht="22.8" spans="1:6">
+      <c r="A144" s="17"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
       <c r="E144" s="14"/>
     </row>
-    <row r="145" s="10" customFormat="1" ht="22.5" spans="1:5">
-      <c r="A145" s="16"/>
+    <row r="145" s="10" customFormat="1" ht="22.8" spans="1:5">
+      <c r="A145" s="15"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
       <c r="E145" s="14"/>
     </row>
-    <row r="146" s="10" customFormat="1" ht="22.5" spans="1:5">
-      <c r="A146" s="19"/>
+    <row r="146" s="10" customFormat="1" ht="22.8" spans="1:5">
+      <c r="A146" s="18"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
       <c r="E146" s="14"/>
     </row>
-    <row r="147" s="10" customFormat="1" ht="22.5" spans="1:5">
-      <c r="A147" s="19"/>
+    <row r="147" s="10" customFormat="1" ht="22.8" spans="1:5">
+      <c r="A147" s="18"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
       <c r="E147" s="14"/>
     </row>
-    <row r="148" s="10" customFormat="1" ht="22.5" spans="1:5">
-      <c r="A148" s="19"/>
+    <row r="148" s="10" customFormat="1" ht="22.8" spans="1:5">
+      <c r="A148" s="18"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
       <c r="E148" s="14"/>
     </row>
-    <row r="149" s="10" customFormat="1" ht="22.5" spans="1:5">
-      <c r="A149" s="19"/>
+    <row r="149" s="10" customFormat="1" ht="22.8" spans="1:5">
+      <c r="A149" s="18"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
       <c r="E149" s="14"/>
     </row>
-    <row r="150" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="150" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E150" s="14"/>
     </row>
-    <row r="151" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="151" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E151" s="14"/>
     </row>
-    <row r="152" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="152" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E152" s="14"/>
     </row>
-    <row r="153" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="153" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E153" s="14"/>
     </row>
-    <row r="154" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="154" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E154" s="14"/>
     </row>
-    <row r="155" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="155" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E155" s="14"/>
     </row>
-    <row r="156" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="156" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E156" s="14"/>
     </row>
-    <row r="157" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="157" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E157" s="14"/>
     </row>
-    <row r="158" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="158" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E158" s="14"/>
     </row>
-    <row r="159" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="159" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E159" s="14"/>
     </row>
-    <row r="160" s="10" customFormat="1" ht="22.5" spans="1:5">
+    <row r="160" s="10" customFormat="1" ht="22.8" spans="1:5">
       <c r="E160" s="14"/>
     </row>
   </sheetData>
@@ -2436,15 +2443,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="68.625" customWidth="1"/>
-    <col min="3" max="3" width="116.6" customWidth="1"/>
-    <col min="4" max="4" width="39.1083333333333" customWidth="1"/>
-    <col min="5" max="5" width="55.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="57.05" customWidth="1"/>
-    <col min="8" max="11" width="12.6333333333333"/>
+    <col min="2" max="2" width="68.6296296296296" customWidth="1"/>
+    <col min="3" max="3" width="193.333333333333" customWidth="1"/>
+    <col min="4" max="4" width="39.1111111111111" customWidth="1"/>
+    <col min="5" max="5" width="86.4537037037037" customWidth="1"/>
+    <col min="6" max="6" width="57.0462962962963" customWidth="1"/>
+    <col min="8" max="11" width="12.6296296296296"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="36" spans="1:6">
@@ -2507,7 +2514,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" ht="36.75" spans="1:6">
+    <row r="4" s="4" customFormat="1" ht="36.6" spans="1:6">
       <c r="A4" s="8">
         <v>101</v>
       </c>
@@ -2549,13 +2556,13 @@
         <v>59</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="9">
         <v>12</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" s="5" customFormat="1" ht="36" spans="1:6">
@@ -2563,16 +2570,16 @@
         <v>104</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" s="5">
         <v>12</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" s="5" customFormat="1" ht="36" spans="1:6">
@@ -2580,16 +2587,16 @@
         <v>105</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D8" s="5">
         <v>12</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" s="5" customFormat="1" ht="36" spans="1:6">
@@ -2597,16 +2604,16 @@
         <v>106</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D9" s="5">
         <v>12</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" s="5" customFormat="1" ht="36" spans="1:6">
@@ -2614,16 +2621,16 @@
         <v>107</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D10" s="5">
         <v>12</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" customFormat="1" ht="19" customHeight="1"/>
@@ -2638,33 +2645,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.90833333333333" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.90740740740741" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.8416666666667" customWidth="1"/>
-    <col min="2" max="2" width="28.0333333333333" customWidth="1"/>
+    <col min="1" max="1" width="35.8425925925926" customWidth="1"/>
+    <col min="2" max="2" width="28.037037037037" customWidth="1"/>
     <col min="3" max="3" width="56.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="16.5" spans="1:3">
+    <row r="1" customFormat="1" ht="15.6" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" ht="66" spans="1:3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" ht="62.4" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="25" customHeight="1" spans="1:3">

--- a/配置文档/ItemConfig.xlsx
+++ b/配置文档/ItemConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GameDev\Roblox_Y1\配置文档\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lanran\Desktop\Gamedev\Roblox_Y1\配置文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="77">
   <si>
     <t>子配置键</t>
   </si>
@@ -163,7 +163,7 @@
     <t>Time=1800</t>
   </si>
   <si>
-    <t>NpcCard</t>
+    <t>DogCard</t>
   </si>
   <si>
     <t>名字</t>
@@ -248,12 +248,6 @@
   </si>
   <si>
     <t>rbxassetid://117314008364013</t>
-  </si>
-  <si>
-    <t>NPC进度卡</t>
-  </si>
-  <si>
-    <t>NPC任务进度加1</t>
   </si>
   <si>
     <t>KeyType, ValueType</t>
@@ -1371,17 +1365,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="23.4537037037037" customWidth="1"/>
-    <col min="3" max="3" width="27.0925925925926" customWidth="1"/>
-    <col min="4" max="4" width="29.3703703703704" customWidth="1"/>
-    <col min="5" max="5" width="31.8148148148148" customWidth="1"/>
+    <col min="2" max="2" width="23.45" customWidth="1"/>
+    <col min="3" max="3" width="27.0916666666667" customWidth="1"/>
+    <col min="4" max="4" width="29.3666666666667" customWidth="1"/>
+    <col min="5" max="5" width="31.8166666666667" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="22.2" spans="1:8">
+    <row r="1" customFormat="1" ht="22.5" spans="1:8">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1399,7 +1393,7 @@
       </c>
       <c r="F1" s="19"/>
     </row>
-    <row r="2" customFormat="1" ht="22.2" spans="1:8">
+    <row r="2" customFormat="1" ht="22.5" spans="1:8">
       <c r="A2" s="19" t="s">
         <v>5</v>
       </c>
@@ -1419,7 +1413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="22.2" spans="1:8">
+    <row r="3" customFormat="1" ht="22.5" spans="1:8">
       <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
@@ -1439,7 +1433,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="22.2" spans="1:8">
+    <row r="4" customFormat="1" ht="22.5" spans="1:8">
       <c r="A4" s="19" t="s">
         <v>12</v>
       </c>
@@ -1461,7 +1455,7 @@
       <c r="G4" s="19"/>
       <c r="H4" s="19"/>
     </row>
-    <row r="5" customFormat="1" ht="22.2" spans="1:8">
+    <row r="5" customFormat="1" ht="22.5" spans="1:8">
       <c r="A5" s="19"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -1471,7 +1465,7 @@
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
     </row>
-    <row r="6" customFormat="1" ht="22.2" spans="1:8">
+    <row r="6" customFormat="1" ht="22.5" spans="1:8">
       <c r="A6" s="19"/>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -1481,7 +1475,7 @@
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
     </row>
-    <row r="7" customFormat="1" ht="22.2" spans="1:8">
+    <row r="7" customFormat="1" ht="22.5" spans="1:8">
       <c r="A7" s="19"/>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -1502,20 +1496,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G160"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.6296296296296" style="10" customWidth="1"/>
+    <col min="1" max="1" width="11.6333333333333" style="10" customWidth="1"/>
     <col min="2" max="2" width="35.5" style="10" customWidth="1"/>
-    <col min="3" max="3" width="11.9074074074074" style="10" customWidth="1"/>
-    <col min="4" max="4" width="43.9259259259259" style="10" customWidth="1"/>
-    <col min="5" max="5" width="24.6296296296296" style="10" customWidth="1"/>
-    <col min="6" max="6" width="33.7962962962963" style="10" customWidth="1"/>
+    <col min="3" max="3" width="11.9083333333333" style="10" customWidth="1"/>
+    <col min="4" max="4" width="43.925" style="10" customWidth="1"/>
+    <col min="5" max="5" width="24.6333333333333" style="10" customWidth="1"/>
+    <col min="6" max="6" width="33.8" style="10" customWidth="1"/>
     <col min="7" max="7" width="60.75" style="10" customWidth="1"/>
-    <col min="8" max="8" width="30.1388888888889" style="10" customWidth="1"/>
+    <col min="8" max="8" width="30.1416666666667" style="10" customWidth="1"/>
     <col min="9" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" ht="22.8" spans="1:7">
+    <row r="1" s="10" customFormat="1" ht="22.5" spans="1:7">
       <c r="A1" s="12" t="s">
         <v>16</v>
       </c>
@@ -1538,7 +1532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" s="10" customFormat="1" ht="22.8" spans="1:7">
+    <row r="2" s="10" customFormat="1" ht="22.5" spans="1:7">
       <c r="A2" s="12" t="s">
         <v>8</v>
       </c>
@@ -1561,7 +1555,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" s="10" customFormat="1" ht="22.8" spans="1:7">
+    <row r="3" s="10" customFormat="1" ht="22.5" spans="1:7">
       <c r="A3" s="12" t="s">
         <v>28</v>
       </c>
@@ -1584,7 +1578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" s="10" customFormat="1" ht="22.8" spans="1:7">
+    <row r="4" s="10" customFormat="1" ht="22.5" spans="1:7">
       <c r="A4" s="13">
         <v>101</v>
       </c>
@@ -1605,7 +1599,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="5" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A5" s="14">
         <v>102</v>
       </c>
@@ -1626,7 +1620,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="6" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A6" s="14">
         <v>103</v>
       </c>
@@ -1641,7 +1635,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="7" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A7" s="14">
         <v>104</v>
       </c>
@@ -1662,7 +1656,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="8" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A8" s="14">
         <v>105</v>
       </c>
@@ -1683,7 +1677,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="9" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A9" s="14">
         <v>106</v>
       </c>
@@ -1704,7 +1698,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="10" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A10" s="14">
         <v>107</v>
       </c>
@@ -1721,433 +1715,433 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="11" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A11" s="14"/>
     </row>
-    <row r="12" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="12" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A12" s="14"/>
     </row>
-    <row r="13" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="13" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A13" s="14"/>
     </row>
-    <row r="14" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="14" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A14" s="14"/>
     </row>
-    <row r="15" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="15" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A15" s="14"/>
     </row>
-    <row r="16" s="11" customFormat="1" ht="22.8" spans="1:7">
+    <row r="16" s="11" customFormat="1" ht="22.5" spans="1:7">
       <c r="A16" s="14"/>
     </row>
-    <row r="17" s="11" customFormat="1" ht="22.8" spans="1:1">
+    <row r="17" s="11" customFormat="1" ht="22.5" spans="1:1">
       <c r="A17" s="14"/>
     </row>
-    <row r="18" s="11" customFormat="1" ht="22.8" spans="1:1">
+    <row r="18" s="11" customFormat="1" ht="22.5" spans="1:1">
       <c r="A18" s="14"/>
     </row>
-    <row r="19" s="11" customFormat="1" ht="22.8" spans="1:1">
+    <row r="19" s="11" customFormat="1" ht="22.5" spans="1:1">
       <c r="A19" s="14"/>
     </row>
-    <row r="20" s="11" customFormat="1" ht="22.8" spans="1:1">
+    <row r="20" s="11" customFormat="1" ht="22.5" spans="1:1">
       <c r="A20" s="14"/>
     </row>
-    <row r="21" s="11" customFormat="1" ht="22.8" spans="1:1">
+    <row r="21" s="11" customFormat="1" ht="22.5" spans="1:1">
       <c r="A21" s="14"/>
     </row>
-    <row r="22" s="11" customFormat="1" ht="22.8" spans="1:1">
+    <row r="22" s="11" customFormat="1" ht="22.5" spans="1:1">
       <c r="A22" s="14"/>
     </row>
-    <row r="23" s="11" customFormat="1" ht="22.8" spans="1:1">
+    <row r="23" s="11" customFormat="1" ht="22.5" spans="1:1">
       <c r="A23" s="14"/>
     </row>
-    <row r="24" s="11" customFormat="1" ht="22.8" spans="1:1">
+    <row r="24" s="11" customFormat="1" ht="22.5" spans="1:1">
       <c r="A24" s="14"/>
     </row>
-    <row r="25" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="25" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A25" s="14"/>
     </row>
-    <row r="26" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="26" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A26" s="14"/>
     </row>
-    <row r="27" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="27" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A27" s="14"/>
     </row>
-    <row r="28" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="28" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A28" s="14"/>
     </row>
-    <row r="29" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="29" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A29" s="14"/>
     </row>
-    <row r="30" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="30" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A30" s="14"/>
     </row>
-    <row r="31" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="31" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A31" s="14"/>
     </row>
-    <row r="32" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="32" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A32" s="14"/>
     </row>
-    <row r="33" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="33" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A33" s="14"/>
     </row>
-    <row r="34" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="34" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A34" s="14"/>
     </row>
-    <row r="35" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="35" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A35" s="14"/>
     </row>
-    <row r="36" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="36" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A36" s="14"/>
     </row>
-    <row r="37" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="37" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A37" s="14"/>
     </row>
-    <row r="38" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="38" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A38" s="14"/>
     </row>
-    <row r="39" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="39" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A39" s="14"/>
     </row>
-    <row r="40" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="40" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A40" s="14"/>
     </row>
-    <row r="41" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="41" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A41" s="14"/>
     </row>
-    <row r="42" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="42" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A42" s="14"/>
     </row>
-    <row r="43" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="43" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A43" s="14"/>
     </row>
-    <row r="44" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="44" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A44" s="14"/>
     </row>
-    <row r="45" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="45" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A45" s="14"/>
     </row>
-    <row r="46" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="46" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A46" s="14"/>
     </row>
-    <row r="47" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="47" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A47" s="14"/>
     </row>
-    <row r="48" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="48" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A48" s="14"/>
     </row>
-    <row r="49" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="49" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A49" s="14"/>
     </row>
-    <row r="50" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="50" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A50" s="14"/>
     </row>
-    <row r="51" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="51" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A51" s="14"/>
     </row>
-    <row r="52" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="52" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A52" s="14"/>
     </row>
-    <row r="53" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="53" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A53" s="14"/>
     </row>
-    <row r="54" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="54" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A54" s="14"/>
     </row>
-    <row r="55" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="55" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A55" s="14"/>
     </row>
-    <row r="56" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="56" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A56" s="14"/>
     </row>
-    <row r="57" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="57" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A57" s="14"/>
     </row>
-    <row r="58" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="58" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A58" s="14"/>
     </row>
-    <row r="59" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="59" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A59" s="14"/>
     </row>
-    <row r="60" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="60" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A60" s="14"/>
     </row>
-    <row r="61" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="61" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A61" s="14"/>
     </row>
-    <row r="62" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="62" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A62" s="14"/>
     </row>
-    <row r="63" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="63" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A63" s="14"/>
     </row>
-    <row r="64" s="10" customFormat="1" ht="22.8" spans="1:1">
+    <row r="64" s="10" customFormat="1" ht="22.5" spans="1:1">
       <c r="A64" s="14"/>
     </row>
-    <row r="65" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="65" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A65" s="14"/>
     </row>
     <row r="66" s="10" customFormat="1" ht="16" customHeight="1" spans="1:6">
       <c r="A66" s="14"/>
     </row>
-    <row r="67" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="67" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A67" s="14"/>
     </row>
-    <row r="68" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="68" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A68" s="14"/>
     </row>
-    <row r="69" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="69" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A69" s="14"/>
     </row>
-    <row r="70" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="70" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A70" s="14"/>
     </row>
-    <row r="71" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="71" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A71" s="14"/>
     </row>
-    <row r="72" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="72" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A72" s="14"/>
     </row>
-    <row r="73" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="73" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A73" s="14"/>
     </row>
-    <row r="74" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="74" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A74" s="14"/>
     </row>
-    <row r="75" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="75" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A75" s="14"/>
     </row>
-    <row r="76" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="76" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A76" s="15"/>
     </row>
-    <row r="77" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="77" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A77" s="15"/>
     </row>
-    <row r="78" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="78" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A78" s="14"/>
     </row>
-    <row r="80" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="80" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
       <c r="E80" s="14"/>
       <c r="F80" s="14"/>
     </row>
-    <row r="81" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="81" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
       <c r="E81" s="14"/>
       <c r="F81" s="14"/>
     </row>
-    <row r="82" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="82" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="14"/>
     </row>
-    <row r="83" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="83" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
       <c r="E83" s="14"/>
       <c r="F83" s="14"/>
     </row>
-    <row r="84" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="84" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
       <c r="E84" s="14"/>
       <c r="F84" s="14"/>
     </row>
-    <row r="85" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="85" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
       <c r="E85" s="14"/>
       <c r="F85" s="14"/>
     </row>
-    <row r="86" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="86" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
     </row>
-    <row r="87" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="87" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
       <c r="E87" s="14"/>
       <c r="F87" s="14"/>
     </row>
-    <row r="88" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="88" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
       <c r="E88" s="14"/>
       <c r="F88" s="14"/>
     </row>
-    <row r="89" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="89" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="14"/>
     </row>
-    <row r="90" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="90" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
       <c r="E90" s="14"/>
       <c r="F90" s="14"/>
     </row>
-    <row r="91" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="91" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
       <c r="E91" s="14"/>
       <c r="F91" s="14"/>
     </row>
-    <row r="92" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="92" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
       <c r="E92" s="14"/>
       <c r="F92" s="14"/>
     </row>
-    <row r="93" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="93" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
       <c r="E93" s="14"/>
       <c r="F93" s="14"/>
     </row>
-    <row r="94" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="94" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
       <c r="E94" s="14"/>
       <c r="F94" s="14"/>
     </row>
-    <row r="95" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="95" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
       <c r="F95" s="16"/>
     </row>
-    <row r="96" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="96" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
       <c r="F96" s="16"/>
     </row>
-    <row r="97" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="97" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
       <c r="E97" s="14"/>
       <c r="F97" s="16"/>
     </row>
-    <row r="98" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="98" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
       <c r="E98" s="14"/>
       <c r="F98" s="14"/>
     </row>
-    <row r="99" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="99" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
       <c r="E99" s="14"/>
       <c r="F99" s="14"/>
     </row>
-    <row r="100" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="100" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
       <c r="E100" s="14"/>
       <c r="F100" s="14"/>
     </row>
-    <row r="101" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="101" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
       <c r="E101" s="14"/>
       <c r="F101" s="14"/>
     </row>
-    <row r="102" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="102" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C102" s="14"/>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
       <c r="F102" s="14"/>
     </row>
-    <row r="103" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="103" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
       <c r="E103" s="14"/>
       <c r="F103" s="14"/>
     </row>
-    <row r="104" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="104" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
       <c r="F104" s="14"/>
     </row>
-    <row r="105" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="105" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
       <c r="E105" s="14"/>
       <c r="F105" s="14"/>
     </row>
-    <row r="106" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="106" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
       <c r="E106" s="14"/>
       <c r="F106" s="14"/>
     </row>
-    <row r="107" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="107" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
       <c r="E107" s="14"/>
       <c r="F107" s="14"/>
     </row>
-    <row r="108" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="108" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
       <c r="F108" s="14"/>
     </row>
-    <row r="109" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="109" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
       <c r="F109" s="14"/>
     </row>
-    <row r="110" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="110" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
       <c r="E110" s="14"/>
       <c r="F110" s="14"/>
     </row>
-    <row r="111" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="111" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
       <c r="E111" s="14"/>
       <c r="F111" s="14"/>
     </row>
-    <row r="112" s="10" customFormat="1" ht="22.8" spans="3:6">
+    <row r="112" s="10" customFormat="1" ht="22.5" spans="3:6">
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
       <c r="E112" s="14"/>
       <c r="F112" s="14"/>
     </row>
-    <row r="113" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="113" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
       <c r="E113" s="14"/>
       <c r="F113" s="14"/>
     </row>
-    <row r="114" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="114" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
       <c r="E114" s="14"/>
       <c r="F114" s="14"/>
     </row>
-    <row r="115" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="115" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
       <c r="E115" s="14"/>
       <c r="F115" s="14"/>
     </row>
-    <row r="116" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="116" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
       <c r="E116" s="14"/>
       <c r="F116" s="14"/>
     </row>
-    <row r="117" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="117" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A117" s="15"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -2155,7 +2149,7 @@
       <c r="E117" s="14"/>
       <c r="F117" s="14"/>
     </row>
-    <row r="118" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="118" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A118" s="15"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -2163,7 +2157,7 @@
       <c r="E118" s="14"/>
       <c r="F118" s="14"/>
     </row>
-    <row r="119" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="119" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A119" s="15"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -2171,7 +2165,7 @@
       <c r="E119" s="14"/>
       <c r="F119" s="14"/>
     </row>
-    <row r="120" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="120" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A120" s="15"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -2179,7 +2173,7 @@
       <c r="E120" s="14"/>
       <c r="F120" s="14"/>
     </row>
-    <row r="121" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="121" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A121" s="15"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -2187,7 +2181,7 @@
       <c r="E121" s="14"/>
       <c r="F121" s="14"/>
     </row>
-    <row r="122" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="122" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A122" s="15"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -2195,7 +2189,7 @@
       <c r="E122" s="14"/>
       <c r="F122" s="14"/>
     </row>
-    <row r="123" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="123" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A123" s="15"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -2203,7 +2197,7 @@
       <c r="E123" s="14"/>
       <c r="F123" s="14"/>
     </row>
-    <row r="124" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="124" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A124" s="15"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -2211,7 +2205,7 @@
       <c r="E124" s="14"/>
       <c r="F124" s="14"/>
     </row>
-    <row r="125" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="125" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A125" s="15"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -2219,7 +2213,7 @@
       <c r="E125" s="14"/>
       <c r="F125" s="14"/>
     </row>
-    <row r="126" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="126" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A126" s="15"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -2227,7 +2221,7 @@
       <c r="E126" s="14"/>
       <c r="F126" s="14"/>
     </row>
-    <row r="127" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="127" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A127" s="15"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -2235,7 +2229,7 @@
       <c r="E127" s="14"/>
       <c r="F127" s="14"/>
     </row>
-    <row r="128" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="128" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A128" s="15"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -2243,7 +2237,7 @@
       <c r="E128" s="14"/>
       <c r="F128" s="14"/>
     </row>
-    <row r="129" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="129" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A129" s="15"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -2251,7 +2245,7 @@
       <c r="E129" s="14"/>
       <c r="F129" s="14"/>
     </row>
-    <row r="130" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="130" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A130" s="15"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -2259,7 +2253,7 @@
       <c r="E130" s="14"/>
       <c r="F130" s="14"/>
     </row>
-    <row r="131" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="131" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A131" s="15"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -2267,7 +2261,7 @@
       <c r="E131" s="14"/>
       <c r="F131" s="14"/>
     </row>
-    <row r="132" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="132" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A132" s="15"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -2275,7 +2269,7 @@
       <c r="E132" s="14"/>
       <c r="F132" s="14"/>
     </row>
-    <row r="133" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="133" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A133" s="15"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -2283,7 +2277,7 @@
       <c r="E133" s="14"/>
       <c r="F133" s="14"/>
     </row>
-    <row r="134" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="134" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A134" s="15"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -2291,7 +2285,7 @@
       <c r="E134" s="14"/>
       <c r="F134" s="14"/>
     </row>
-    <row r="135" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="135" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A135" s="15"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -2299,7 +2293,7 @@
       <c r="E135" s="14"/>
       <c r="F135" s="14"/>
     </row>
-    <row r="136" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="136" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A136" s="15"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -2307,7 +2301,7 @@
       <c r="E136" s="14"/>
       <c r="F136" s="14"/>
     </row>
-    <row r="137" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="137" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A137" s="15"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -2315,121 +2309,121 @@
       <c r="E137" s="14"/>
       <c r="F137" s="14"/>
     </row>
-    <row r="138" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="138" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A138" s="15"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
       <c r="E138" s="14"/>
     </row>
-    <row r="139" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="139" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A139" s="15"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
       <c r="E139" s="14"/>
     </row>
-    <row r="140" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="140" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A140" s="17"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
       <c r="E140" s="14"/>
     </row>
-    <row r="141" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="141" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A141" s="17"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
       <c r="E141" s="14"/>
     </row>
-    <row r="142" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="142" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A142" s="17"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
       <c r="E142" s="14"/>
     </row>
-    <row r="143" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="143" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A143" s="17"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
       <c r="E143" s="14"/>
     </row>
-    <row r="144" s="10" customFormat="1" ht="22.8" spans="1:6">
+    <row r="144" s="10" customFormat="1" ht="22.5" spans="1:6">
       <c r="A144" s="17"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
       <c r="E144" s="14"/>
     </row>
-    <row r="145" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="145" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="A145" s="15"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
       <c r="E145" s="14"/>
     </row>
-    <row r="146" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="146" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="A146" s="18"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
       <c r="E146" s="14"/>
     </row>
-    <row r="147" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="147" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="A147" s="18"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
       <c r="E147" s="14"/>
     </row>
-    <row r="148" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="148" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="A148" s="18"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
       <c r="E148" s="14"/>
     </row>
-    <row r="149" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="149" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="A149" s="18"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
       <c r="E149" s="14"/>
     </row>
-    <row r="150" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="150" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E150" s="14"/>
     </row>
-    <row r="151" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="151" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E151" s="14"/>
     </row>
-    <row r="152" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="152" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E152" s="14"/>
     </row>
-    <row r="153" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="153" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E153" s="14"/>
     </row>
-    <row r="154" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="154" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E154" s="14"/>
     </row>
-    <row r="155" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="155" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E155" s="14"/>
     </row>
-    <row r="156" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="156" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E156" s="14"/>
     </row>
-    <row r="157" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="157" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E157" s="14"/>
     </row>
-    <row r="158" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="158" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E158" s="14"/>
     </row>
-    <row r="159" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="159" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E159" s="14"/>
     </row>
-    <row r="160" s="10" customFormat="1" ht="22.8" spans="1:5">
+    <row r="160" s="10" customFormat="1" ht="22.5" spans="1:5">
       <c r="E160" s="14"/>
     </row>
   </sheetData>
@@ -2443,15 +2437,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="68.6296296296296" customWidth="1"/>
+    <col min="2" max="2" width="68.6333333333333" customWidth="1"/>
     <col min="3" max="3" width="193.333333333333" customWidth="1"/>
-    <col min="4" max="4" width="39.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="86.4537037037037" customWidth="1"/>
-    <col min="6" max="6" width="57.0462962962963" customWidth="1"/>
-    <col min="8" max="11" width="12.6296296296296"/>
+    <col min="4" max="4" width="39.1083333333333" customWidth="1"/>
+    <col min="5" max="5" width="86.45" customWidth="1"/>
+    <col min="6" max="6" width="57.05" customWidth="1"/>
+    <col min="8" max="11" width="12.6333333333333"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="36" spans="1:6">
@@ -2514,7 +2508,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" ht="36.6" spans="1:6">
+    <row r="4" s="4" customFormat="1" ht="36.75" spans="1:6">
       <c r="A4" s="8">
         <v>101</v>
       </c>
@@ -2621,10 +2615,10 @@
         <v>107</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D10" s="5">
         <v>12</v>
@@ -2645,33 +2639,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.90740740740741" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.90833333333333" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.8425925925926" customWidth="1"/>
-    <col min="2" max="2" width="28.037037037037" customWidth="1"/>
+    <col min="1" max="1" width="35.8416666666667" customWidth="1"/>
+    <col min="2" max="2" width="28.0333333333333" customWidth="1"/>
     <col min="3" max="3" width="56.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="15.6" spans="1:3">
+    <row r="1" customFormat="1" ht="16.5" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" ht="66" spans="1:3">
+      <c r="A2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" ht="62.4" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="25" customHeight="1" spans="1:3">

--- a/配置文档/ItemConfig.xlsx
+++ b/配置文档/ItemConfig.xlsx
@@ -1666,7 +1666,7 @@
       </s:c>
       <s:c r="B10" s="12" t="inlineStr">
         <s:is>
-          <s:t>DogCard</s:t>
+          <s:t>NoobCard</s:t>
         </s:is>
       </s:c>
       <s:c r="C10" s="15" t="n">
@@ -1674,7 +1674,7 @@
       </s:c>
       <s:c r="D10" s="12" t="inlineStr">
         <s:is>
-          <s:t>DogCard</s:t>
+          <s:t>NoobCard</s:t>
         </s:is>
       </s:c>
       <s:c r="E10" s="15" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </s:c>
       <s:c r="B10" s="10" t="inlineStr">
         <s:is>
-          <s:t>Dog Card</s:t>
+          <s:t>Noob Card</s:t>
         </s:is>
       </s:c>
       <s:c r="C10" s="10" t="inlineStr">
         <s:is>
-          <s:t>Adds one progress to today's Dog task.</s:t>
+          <s:t>Adds one progress to today's Noob task.</s:t>
         </s:is>
       </s:c>
       <s:c r="D10" s="6" t="n">

--- a/配置文档/ItemConfig.xlsx
+++ b/配置文档/ItemConfig.xlsx
@@ -2658,7 +2658,7 @@
       </s:c>
       <s:c r="B10" s="10" t="inlineStr">
         <s:is>
-          <s:t>Noob Card</s:t>
+          <s:t>NoobCard</s:t>
         </s:is>
       </s:c>
       <s:c r="C10" s="10" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </s:c>
       <s:c r="E10" s="6" t="inlineStr">
         <s:is>
-          <s:t>rbxassetid://117314008364013</s:t>
+          <s:t>rbxassetid://110509395107513</s:t>
         </s:is>
       </s:c>
     </s:row>
